--- a/AAII_Financials/Quarterly/JLL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JLL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
   <si>
     <t>JLL</t>
   </si>
@@ -656,343 +656,350 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6927900</v>
+      </c>
+      <c r="E8" s="3">
         <v>6386500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7608700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6510400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6250100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5746400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6810900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5868800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5628700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5124500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5881400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5111400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5052500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4715500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5604800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5177500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5278400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4801400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5945700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4889200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4495000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4037100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4845400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3978100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3670400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4096000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5400500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4495600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4266500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3820600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4889700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3969800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3903700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3555200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>4343000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3522200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>3470300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>3117700</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2158200</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1705200</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3419900</v>
+      </c>
+      <c r="E9" s="3">
         <v>3182700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3623500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3152600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3128600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2860500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3226700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2729200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2803300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2532000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2841400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2467000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2414600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2351500</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="R9" s="3" t="s">
         <v>5</v>
@@ -1003,56 +1010,56 @@
       <c r="T9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V9" s="3">
         <v>2342100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2084300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1987500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1907500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2098200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1886700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1841900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1863000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2225500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1949800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1918300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1859000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2068300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1756100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1740400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1664100</v>
-      </c>
-      <c r="AK9" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AL9" s="3" t="s">
         <v>5</v>
@@ -1069,52 +1076,55 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>3508000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3203800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3985200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3357800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3121500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2885900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3584200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3139600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2825400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2592500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3040000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2644400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2637900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2364000</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
@@ -1125,56 +1135,56 @@
       <c r="T10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V10" s="3">
         <v>3603600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2804900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2507500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2129600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2747200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2091400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1828500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2233000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3175000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2545800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2348200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1961600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2821400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2213700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2163300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1891100</v>
-      </c>
-      <c r="AK10" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AL10" s="3" t="s">
         <v>5</v>
@@ -1191,8 +1201,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,252 +1496,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E14" s="3">
         <v>5300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>22600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>11700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>21300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>19700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>18700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-8800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>11500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>21600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>31600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>11800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>35700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>38400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>21000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>25900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>19500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>33800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>15600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>18100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>17200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>66600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>33500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>28200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>14100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>70100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>70000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>25700</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>18600</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>45500</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>3700</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-11100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>700</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>17400</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>3400</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>5400</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>4500</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>32600</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>57200</v>
+      </c>
+      <c r="E15" s="3">
         <v>57800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>55900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>57600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>67700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>71600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>67000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>65500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>62300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>61000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>61900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>59100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>59900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>57500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>62600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>55700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>55400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>54400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>57200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>52800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>54500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>53000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>59600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>54900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>56900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>55000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>56800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>53600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>45500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>46500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>55000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>42700</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>46300</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>42100</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>44900</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>41800</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>41200</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>39300</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>43300</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>35900</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6611300</v>
+      </c>
+      <c r="E17" s="3">
         <v>6176600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7079200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6225000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6031400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5606700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6419000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5649300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5464800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5008600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5569400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4960700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4891500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4662000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5350100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4974900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5043300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4625700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5500100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4596300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4270700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3956400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4516600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3823200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3659600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4031400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5032200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4324000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4116400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3795200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4577300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3778900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3753900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3501400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>4081100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3384400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3339500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1600900</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1931900</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1634200</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>316600</v>
+      </c>
+      <c r="E18" s="3">
         <v>209900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>529500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>285400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>218700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>139700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>391900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>219500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>163900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>115900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>312000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>150700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>161000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>53500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>254700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>202600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>235100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>175700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>445600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>292900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>224300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>80700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>328800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>154900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>10800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>64600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>368300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>171600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>150100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>25400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>312400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>190900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>149800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>53800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>261900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>137800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>130800</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1516800</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>226300</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>71000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,297 +2085,304 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-9900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-9300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-30500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>24900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>23900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>46000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>73800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>8200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>104700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-33400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-22200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>173200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>8500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>91100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>9100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>30000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>49900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>5400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>5000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-42000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-10100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-4900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>8400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-9200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>2300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-2600</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-100</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-1507800</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-7000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>374900</v>
+      </c>
+      <c r="E21" s="3">
         <v>277600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>594700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>373500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>261500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>187400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>412900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>287000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>220500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>174700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>300100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>201600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>116200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>108500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>283900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>236100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>463700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>238600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>593900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>354800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>308800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>183600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>335600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>158300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>17700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>77600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>361400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>179500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>146500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>67000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>333100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>178100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>151600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>98200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>264000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>135800</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>132600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>48300</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>226700</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>68600</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E22" s="3">
         <v>17000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>18200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>29200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>35300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>24600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>26600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>38100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>41700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>30500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>31500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>37100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>40500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>26300</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -2418,252 +2458,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>265600</v>
+      </c>
+      <c r="E23" s="3">
         <v>197500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>498000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>275000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>137200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>71500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>300600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>192200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>105000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>81500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>185100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>73800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>221300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>180400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>408300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>184200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>536700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>302000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>254300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>130600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>330900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>160300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>15800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>22600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>358200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>171400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>147500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>20500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>320800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>181700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>147400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>56100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>260900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>135200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>130700</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>9000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>219300</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>64100</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>51300</v>
+      </c>
+      <c r="E24" s="3">
         <v>38100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>96200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>52600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>26700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>14000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>58700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>37400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>20500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>15900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>12700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>14500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>45400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>42300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>72800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>40300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>115900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>65300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>54900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>28200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>74700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>25700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>86400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>42100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>36200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>70600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>45600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>37600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>13500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>57300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>36000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>35800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>1300</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>52700</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>214300</v>
+      </c>
+      <c r="E26" s="3">
         <v>159400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>401800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>222400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>110500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>57500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>241900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>154800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>84500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>65600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>172400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>59300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>175900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>138100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>335500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>143900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>420800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>236700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>199400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>102400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>256200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>134600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>14300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>17600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>271800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>129300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>111300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>21200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>250200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>136100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>109800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>42600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>203600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>99200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>94900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>7700</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>166600</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>48200</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>215600</v>
+      </c>
+      <c r="E27" s="3">
         <v>159000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>401700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>222800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>112300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>55300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>241200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>155100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>84400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>66100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>172400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>59700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>174800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>140200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>193900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>145600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>421400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>237200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>200000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>103000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>250100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>131900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>15200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>5300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>269400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>128900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>110500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>21300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>248100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>134900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>107800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>40300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>202100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>98300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>94300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>7200</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>165300</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>48000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3212,8 +3273,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>5</v>
@@ -3230,11 +3291,11 @@
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3">
         <v>4300</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
@@ -3242,11 +3303,11 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-47000</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>5</v>
@@ -3254,11 +3315,11 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-125900</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>9900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>9300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>30500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-24900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-23900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-46000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-73800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-8200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-104700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>33400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>22200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-173200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-8500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-91100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-9100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-30000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-49900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-5400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>42000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>10100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>4900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-8400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>9200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>1000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>2600</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>100</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>1507800</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>7000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>215600</v>
+      </c>
+      <c r="E33" s="3">
         <v>159000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>401700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>222800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>112300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>55300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>241200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>155100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>84400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>66100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>172400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>59700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>174800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>140200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>193900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>145600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>421400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>237200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>200000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>103000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>250100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>131900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>15200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>5300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>273700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>128900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>110500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>21300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>201100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>134900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>107800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>40300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>76200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>98300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>94300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>7200</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>165300</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>48000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>215600</v>
+      </c>
+      <c r="E35" s="3">
         <v>159000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>401700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>222800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>112300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>55300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>241200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>155100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>84400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>66100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>172400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>59700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>174800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>140200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>193900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>145600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>421400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>237200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>200000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>103000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>250100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>131900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>15200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>5300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>273700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>128900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>110500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>21300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>201100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>134900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>107800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>40300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>76200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>98300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>94300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>7200</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>165300</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>48000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>458200</v>
+      </c>
+      <c r="E41" s="3">
         <v>436200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>599100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>428900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>401400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>432400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>416300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>437800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>424400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>396700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>410000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>389500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>402500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>485400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>519300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>489400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>568000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>575800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>593700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>535900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>494000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>456600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>574300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>440000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>413500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>720700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>451900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>402200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>411200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>389500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>480900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>327000</v>
-      </c>
-      <c r="AI41" s="3">
-        <v>292800</v>
       </c>
       <c r="AJ41" s="3">
         <v>292800</v>
       </c>
       <c r="AK41" s="3">
+        <v>292800</v>
+      </c>
+      <c r="AL41" s="3">
         <v>268000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>277900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>250300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>223100</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>258500</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>228400</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4463,130 +4553,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6110300</v>
+      </c>
+      <c r="E43" s="3">
         <v>6110100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6197900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5603600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5600800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5619400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5640200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5275800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4984900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5005400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5202200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4671300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4661000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4779200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5446900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5172700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5029500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5022900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5293300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4721600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2993600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2974100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3901000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3926600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2932000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3521300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3367600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3339300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2846500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2779200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2862900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2818300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3826500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3733300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3883900</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2463300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>2883100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>2322000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>2798100</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>2346200</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4629,8 +4725,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4707,618 +4803,636 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>51100</v>
+      </c>
+      <c r="E45" s="3">
         <v>70400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>52200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>43100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>54200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>71400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>161100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>126800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>152300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>139300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>128000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>214100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>198700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>155200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>603500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>707800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>552300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>566700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>500700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1993700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1840400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1843000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1978400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1801900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1763400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1955300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2049100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1848600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1772400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1859000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1862200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1716000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>350500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>363400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>646800</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>245100</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>265900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>251100</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>243100</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>243700</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7825900</v>
+      </c>
+      <c r="E46" s="3">
         <v>8304700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8179400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7642600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7851500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7233700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7478500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8406700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6634000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6315100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6857000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6378600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6705800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6771800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6569700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6369900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6149800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6165400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6387700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7251200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5328000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5273700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6453700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6168500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5108900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6197300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5868600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5590100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5030100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5027700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5206000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4861300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4469800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4389500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4541000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2986300</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>3399300</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>2796200</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>3299700</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>2818300</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>873600</v>
+      </c>
+      <c r="E47" s="3">
         <v>886600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>892900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>895100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>878800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>902400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>812700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>866500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>819700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>816200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>816600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>865200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>872700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>896000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1204900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1196900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1191100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1112800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1062100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>925400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>895500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>794800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>661900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>629400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>644200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>646600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>654400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>650600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>596800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>578800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>555900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>551100</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>555000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>555100</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>540900</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>541100</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>538400</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>539600</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>531800</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>541700</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1305900</v>
+      </c>
+      <c r="E48" s="3">
         <v>1315700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1342900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1333900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1305800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1323500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1341200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1346100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1356300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1344100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1344800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1344700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1346800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1344200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1359200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1508100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1503100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1518300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1463400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1386200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1378100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1388500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1371300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1432200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1475900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1484900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1506300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1349500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1184400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1170600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>567900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>540800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>536400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>561900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>543900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>516600</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>512900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>507000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>501000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>468700</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5362400</v>
+      </c>
+      <c r="E49" s="3">
         <v>5341300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5374000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5376900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5397800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5344300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5335400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5388300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5353100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5331700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5372400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5345000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5398800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5377000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5386500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5316400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5391800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5477400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5498600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4892700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4877600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4888700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4904500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4817900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4773800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4763000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4850800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4758800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3066800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3077000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3034700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2981200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2975700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3046300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>3014300</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>3008700</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>2970900</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>2932500</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>2874300</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>2846300</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1429200</v>
+      </c>
+      <c r="E52" s="3">
         <v>1375000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1338800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1323500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1271700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1233900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1228200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1230300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1185900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1133500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1114400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1099000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1038400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>995700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1073400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>987300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1036500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1118700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1093200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>991900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>975900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>960700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>925100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>854100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>807700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>809000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>792500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>728900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>702800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>698400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>661000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>684700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>650800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>651400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>614300</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>501600</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>476400</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>460700</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>422600</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>441600</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17464200</v>
+      </c>
+      <c r="E54" s="3">
         <v>17888300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>17801100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>17178700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>17340500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16631100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16763800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17817200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15909000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>15482400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16064800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15480500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15825500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15849100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>15593700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>15378600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>15272300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>15392600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>15505000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>15447400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>13455100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>13306400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>14316500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>13902100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>12810500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>13900800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>13672600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>13077900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>10580900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>10552500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>10025500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>9619100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>9187700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>9204200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>9254400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>7554300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>7897900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>7236000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>7629400</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>7116600</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1243100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1223700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1398100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1196100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1184300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1201400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1322700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1162000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1154000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1232800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1406700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1074200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1054600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1110500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1236800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>858400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>947000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1059400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1262800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1011300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1034600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1108700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1229800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1096700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1044800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1096200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1289400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>939000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1037200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>986400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1261400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>995100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>966400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>979700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>993100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>793600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>802000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>806200</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>846200</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>763600</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1563600</v>
+      </c>
+      <c r="E58" s="3">
         <v>2105900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1018300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1705100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2185000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1742800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1351300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3113500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>937300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>604900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>972500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>851000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1218200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1079700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>619500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>929200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1025400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1098200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1218300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2383900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>816600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>924100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1560400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1830200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>904200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1061800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>636000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>886800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>502700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>596500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>350600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>695600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>537900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>501500</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>77400</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>64200</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>69500</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>62500</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>89500</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>55700</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2828500</v>
+      </c>
+      <c r="E59" s="3">
         <v>2754700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3040600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2677800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2661000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2519700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2702000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2386100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2324700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2168500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2368600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2161500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2076700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1953400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4055800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3616100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3364800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3245400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4005400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3275700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2790900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2659000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3337600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2875200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2657500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2829400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3564800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3036900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2630600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2628700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3149800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2644000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2328100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2357100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3273700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1724600</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1980300</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1362200</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>2030600</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>1477500</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6951500</v>
+      </c>
+      <c r="E60" s="3">
         <v>7386900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7386600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6955500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7166200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6626700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7144500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8028000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5514000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5099100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6446100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5425500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5490700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5265200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5912100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5403700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5337200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5403000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6486500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6670900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4642100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4691800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6127800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5802100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4606500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4987400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5490200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4862700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4170500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4211600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4761800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4334700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3832400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>3838300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>4313700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2582400</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2851800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2230900</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>2966300</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>2296800</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1655300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1869600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1605500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1777500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1925600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1935600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1594100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1899600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2809800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2910500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2144400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2725400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2987800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3235100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1586600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1929400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1728700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1501500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>533800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>890800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1024600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1026300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>693300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1073300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1354900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2094700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1177300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1765000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1155500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1174100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>655600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>900500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1076900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1012800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>690600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1117800</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1327100</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1429300</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>1178100</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>1356900</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1190600</v>
+      </c>
+      <c r="E62" s="3">
         <v>1144200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1128500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1100500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1038200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1061200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1082500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1079000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1044400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1019900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1015700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>998900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>963500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>984400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1945500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2036100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2052500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2065400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2063500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1926100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1881200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1873600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1877600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1732600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1731600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1781200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1791800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1583600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1371100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1363300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>873600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>811100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>812200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>877400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>919500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>678800</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>681300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>673900</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>663500</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>608000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9863900</v>
+      </c>
+      <c r="E66" s="3">
         <v>10461700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10178100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9882600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10178900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9669000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9868700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11048200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9410700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9074800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9654900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9310800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9633600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9686800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9572800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9607000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>9359400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9219400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>9320100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>9591700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7645800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7686200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>8795700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>8698400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>7784300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>8953800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>8554500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>8293600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6758900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6810100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6334000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6087100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>5759700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>5769400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>5914300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>4410600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>4892800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>4369700</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>4839700</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>4318800</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7443300</v>
+      </c>
+      <c r="E72" s="3">
         <v>7228100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7114000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6714100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6494700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6383000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6334900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6094600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5941900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5857600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5795600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5624500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5567600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5566700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5590400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5415600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5275400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>5083200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>4937600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>4516100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>4278900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>4078900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3975900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>3725900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>3593900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>3578700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>3588300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>3336700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>3207800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>3117000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>3095700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2913300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2778400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>2689300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>2649000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>2491400</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>2404800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>2342500</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>2333000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>2182700</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7461700</v>
+      </c>
+      <c r="E76" s="3">
         <v>7306900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7502800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7175300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7039900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6839200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6771500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6646900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6379200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6293500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6293800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6044500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6064600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6033800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6020900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5771600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5912900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>6173200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>6184900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5855700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5809300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5620200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5520800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5203700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5026200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4947000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>5118100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4784300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3822000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3742400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3691500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3532000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3428000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3434800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3340100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>3143700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>3005100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>2866300</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>2789700</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>2797800</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>215600</v>
+      </c>
+      <c r="E81" s="3">
         <v>159000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>401700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>222800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>112300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>55300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>241200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>155100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>84400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>66100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>172400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>59700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>174800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>140200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>193900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>145600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>421400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>237200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>200000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>103000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>250100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>131900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>15200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>5300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>273700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>128900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>110500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>21300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>201100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>134900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>107800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>40300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>76200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>98300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>94300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>7200</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>165300</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>48000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,76 +8990,77 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>50700</v>
+      </c>
+      <c r="E83" s="3">
         <v>54600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>50200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>48900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>45600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>44800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>44700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>41900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>41800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>40000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>43800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>37900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>38500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>37600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>62600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>55700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>55400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>54400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>57200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>52800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>54500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>53000</v>
-      </c>
-      <c r="Y83" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="Z83" s="3" t="s">
         <v>5</v>
@@ -8878,8 +9077,8 @@
       <c r="AD83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE83" s="3">
-        <v>0</v>
+      <c r="AE83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AF83" s="3">
         <v>0</v>
@@ -8914,8 +9113,11 @@
       <c r="AP83" s="3">
         <v>0</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>488100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-755000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1011800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>617100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>332800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-767600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>927300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>261600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>273900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-677500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>729400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>325700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>237000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-716300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>601800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>137500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>177000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-716400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>762100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>456400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>215700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-461800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>751600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>407800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>501400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-546100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>735300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>231600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>68400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-551500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>604400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>267600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-9300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-258600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>503000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>310500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>196800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-211600</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>366400</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>130900</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-50100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-64900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-77200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-49500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-44400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-44500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-59200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-44900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-38200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-43200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-49200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-49500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-38900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-49300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-69800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-49100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-40300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-46600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-64300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-41800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-35200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-34600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-36900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-35200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-32900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-44400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>51900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-47300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-39200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-44600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AH91" s="3">
-        <v>0</v>
-      </c>
       <c r="AI91" s="3">
         <v>0</v>
       </c>
       <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-34900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>95800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-34900</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-31600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-63200</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-112900</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-88900</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-64200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-61300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-85000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-51200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-47600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-152800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-97800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-64900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-99800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-54300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-70000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-59700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-86700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-74000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-95300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-84700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>30900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-94000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-489800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-102200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-116000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-97800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-46400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-14800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-18900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-90500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-55600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-852400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-50700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-91000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-133200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-63500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-23700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-60000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-47000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-35800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-40400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-43500</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-184600</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-418300</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,8 +10455,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10266,8 +10500,8 @@
       <c r="P96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10303,11 +10537,11 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-22800</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
@@ -10315,11 +10549,11 @@
         <v>0</v>
       </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-18900</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
         <v>0</v>
       </c>
@@ -10327,11 +10561,11 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-17000</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
         <v>0</v>
       </c>
@@ -10339,13 +10573,16 @@
         <v>0</v>
       </c>
       <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-15200</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-397600</v>
+      </c>
+      <c r="E100" s="3">
         <v>649400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-716000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-544700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-283200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>900700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-800200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-217600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-136800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>703400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-605500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-272700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-271400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>775300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-513600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-100800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-205200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>806500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-183100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-275400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-62000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>376700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-527400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-357900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-769200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>883300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-610000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>647100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-45300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>592800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-313800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-210700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>41400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>341800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-458100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-249700</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-132600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>216900</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-142900</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>301800</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E101" s="3">
         <v>11700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-26200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>12900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-9700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>15900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-13400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>4500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>24300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-26000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-30900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>24300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-26000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-30900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-6700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-3700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-7600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-12400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>19100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>10800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>6000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-21100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>8600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-11300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-6500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-16400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>2000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>1900</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>2400</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>4900</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>4100</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-8800</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-179600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>211500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>16900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>25800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-8000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>32300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-38100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>69800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-20100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-121800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>17200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-74000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-28200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-10600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>85500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>71200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>40400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-195300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>196900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>45900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-280700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>225600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>78300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>15000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-26400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-49000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>158400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-13100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-8000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>25200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>27600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>27200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-35400</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>30100</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>14700</v>
       </c>
     </row>
